--- a/notebooks/solutions/credit_solution_min_bad_count.xlsx
+++ b/notebooks/solutions/credit_solution_min_bad_count.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,7 +513,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>313</v>
@@ -522,7 +522,7 @@
         <v>35</v>
       </c>
       <c r="M2" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,7 +552,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>206</v>
@@ -561,7 +561,7 @@
         <v>99</v>
       </c>
       <c r="M3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -702,7 +702,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -724,7 +724,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>240</v>
@@ -733,7 +733,7 @@
         <v>29</v>
       </c>
       <c r="M7" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -745,7 +745,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -767,7 +767,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>242</v>
@@ -776,7 +776,7 @@
         <v>40</v>
       </c>
       <c r="M8" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -788,7 +788,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -810,7 +810,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>218</v>
@@ -819,7 +819,7 @@
         <v>44</v>
       </c>
       <c r="M9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -831,7 +831,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -853,7 +853,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>212</v>
@@ -862,7 +862,7 @@
         <v>63</v>
       </c>
       <c r="M10" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1111,7 +1111,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>316</v>
@@ -1120,7 +1120,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1154,7 +1154,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>289</v>
@@ -1163,7 +1163,7 @@
         <v>33</v>
       </c>
       <c r="M17" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>234</v>
@@ -1206,7 +1206,7 @@
         <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1283,7 +1283,7 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>274</v>
@@ -1292,7 +1292,7 @@
         <v>67</v>
       </c>
       <c r="M20" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1412,7 +1412,7 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>370</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>370</v>
@@ -1421,7 +1421,7 @@
         <v>73</v>
       </c>
       <c r="M23" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1455,7 +1455,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>267</v>
@@ -1464,7 +1464,7 @@
         <v>32</v>
       </c>
       <c r="M24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1498,7 +1498,7 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>234</v>
@@ -1507,7 +1507,7 @@
         <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1541,7 +1541,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>224</v>
@@ -1550,7 +1550,7 @@
         <v>39</v>
       </c>
       <c r="M26" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1584,7 +1584,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>341</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>341</v>
@@ -1593,7 +1593,7 @@
         <v>82</v>
       </c>
       <c r="M27" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1627,7 +1627,7 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>344</v>
@@ -1636,7 +1636,7 @@
         <v>37</v>
       </c>
       <c r="M28" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1670,7 +1670,7 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>389</v>
@@ -1679,7 +1679,7 @@
         <v>66</v>
       </c>
       <c r="M29" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1713,7 +1713,7 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>368</v>
@@ -1722,7 +1722,7 @@
         <v>93</v>
       </c>
       <c r="M30" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1756,7 +1756,7 @@
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>422</v>
@@ -1765,7 +1765,7 @@
         <v>61</v>
       </c>
       <c r="M31" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1799,7 +1799,7 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>427</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>427</v>
@@ -1808,7 +1808,7 @@
         <v>58</v>
       </c>
       <c r="M32" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1842,7 +1842,7 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>214</v>
@@ -1851,7 +1851,7 @@
         <v>47</v>
       </c>
       <c r="M33" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1885,7 +1885,7 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>433</v>
@@ -1894,7 +1894,7 @@
         <v>176</v>
       </c>
       <c r="M34" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1928,7 +1928,7 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>468</v>
@@ -1937,7 +1937,7 @@
         <v>200</v>
       </c>
       <c r="M35" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1971,7 +1971,7 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>352</v>
@@ -1980,7 +1980,7 @@
         <v>194</v>
       </c>
       <c r="M36" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2065,7 +2065,7 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>229</v>
@@ -2074,7 +2074,7 @@
         <v>21</v>
       </c>
       <c r="M38" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2206,7 +2206,7 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>306</v>
@@ -2215,7 +2215,7 @@
         <v>48</v>
       </c>
       <c r="M41" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2300,7 +2300,7 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>247</v>
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="M43" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2394,7 +2394,7 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>284</v>
@@ -2403,7 +2403,7 @@
         <v>44</v>
       </c>
       <c r="M45" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2441,7 +2441,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>367</v>
@@ -2450,7 +2450,7 @@
         <v>38</v>
       </c>
       <c r="M46" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2488,7 +2488,7 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
-        <v>254</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>254</v>
@@ -2497,7 +2497,7 @@
         <v>45</v>
       </c>
       <c r="M47" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2582,7 +2582,7 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>201</v>
@@ -2591,7 +2591,7 @@
         <v>35</v>
       </c>
       <c r="M49" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2629,7 +2629,7 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>202</v>
@@ -2638,7 +2638,7 @@
         <v>23</v>
       </c>
       <c r="M50" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2676,7 +2676,7 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>334</v>
@@ -2685,7 +2685,7 @@
         <v>47</v>
       </c>
       <c r="M51" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2723,7 +2723,7 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>472</v>
@@ -2732,7 +2732,7 @@
         <v>96</v>
       </c>
       <c r="M52" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2770,7 +2770,7 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>215</v>
@@ -2779,7 +2779,7 @@
         <v>31</v>
       </c>
       <c r="M53" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2817,7 +2817,7 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
-        <v>262</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>262</v>
@@ -2826,7 +2826,7 @@
         <v>58</v>
       </c>
       <c r="M54" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2864,7 +2864,7 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>200</v>
@@ -2873,7 +2873,7 @@
         <v>38</v>
       </c>
       <c r="M55" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2911,7 +2911,7 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>220</v>
@@ -2920,7 +2920,7 @@
         <v>59</v>
       </c>
       <c r="M56" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2958,7 +2958,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>344</v>
@@ -2967,7 +2967,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3052,7 +3052,7 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>408</v>
@@ -3061,7 +3061,7 @@
         <v>78</v>
       </c>
       <c r="M59" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3099,7 +3099,7 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>200</v>
@@ -3108,7 +3108,7 @@
         <v>84</v>
       </c>
       <c r="M60" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3146,7 +3146,7 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>554</v>
@@ -3155,7 +3155,7 @@
         <v>400</v>
       </c>
       <c r="M61" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3193,7 +3193,7 @@
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
         <v>339</v>
@@ -3202,7 +3202,7 @@
         <v>284</v>
       </c>
       <c r="M62" t="n">
-        <v>284</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3240,7 +3240,7 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>310</v>
@@ -3249,7 +3249,7 @@
         <v>195</v>
       </c>
       <c r="M63" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3287,7 +3287,7 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>265</v>
@@ -3296,7 +3296,7 @@
         <v>200</v>
       </c>
       <c r="M64" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>435</v>
@@ -3347,7 +3347,7 @@
         <v>109</v>
       </c>
       <c r="M65" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>268</v>
@@ -3398,7 +3398,7 @@
         <v>93</v>
       </c>
       <c r="M66" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>234</v>
@@ -3449,7 +3449,7 @@
         <v>173</v>
       </c>
       <c r="M67" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>313</v>
@@ -3500,7 +3500,7 @@
         <v>60</v>
       </c>
       <c r="M68" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>221</v>
@@ -3551,7 +3551,7 @@
         <v>76</v>
       </c>
       <c r="M69" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>230</v>
@@ -3755,7 +3755,7 @@
         <v>34</v>
       </c>
       <c r="M73" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>226</v>
@@ -3810,7 +3810,7 @@
         <v>130</v>
       </c>
       <c r="M74" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>200</v>
@@ -3865,7 +3865,7 @@
         <v>144</v>
       </c>
       <c r="M75" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3879,7 +3879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2212</v>
+        <v>0.06727783528020109</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -3943,7 +3943,9 @@
           <t>Reject</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>0.2873482874753765</v>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -3951,16 +3953,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>kAcceptedRatio</t>
+          <t>kBadRatio</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.2212</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -3974,17 +3976,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reject</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>0.2</v>
-      </c>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>n/a (empty)</t>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>kAcceptedRatio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>kAcceptedRatio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.3005777777777778</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4067,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mBadCount</t>
+          <t>mAcceptedBadCount</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4036,7 +4076,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4977</v>
+        <v>455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4305,7 +4345,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>decision=Reject min=0.2 max=None</t>
+          <t>decision=TOTAL min=0.3 max=None</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4357,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mBadCount</t>
+          <t>mAcceptedBadCount</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
